--- a/output/pdf_financials_xlsx/SRC.xlsx
+++ b/output/pdf_financials_xlsx/SRC.xlsx
@@ -971,28 +971,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>2e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.005261</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00033</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000594</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000469</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.006448</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.001247</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.706861</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-1.386302</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1864,28 +1864,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.164835</v>
+        <v>-0.164855</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.136803</v>
+        <v>-2.142064</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.831072</v>
+        <v>-0.831402</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.711288</v>
+        <v>-0.711882</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.501271</v>
+        <v>-2.50174</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.275</v>
+        <v>-2.281448</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.266993</v>
+        <v>-2.26824</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.706861</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.566947</v>
@@ -1897,7 +1897,7 @@
         <v>-0.031616</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.386302</v>
+        <v>0</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -1970,28 +1970,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.164835</v>
+        <v>-0.164855</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.136803</v>
+        <v>-2.142064</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.831072</v>
+        <v>-0.831402</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.711288</v>
+        <v>-0.711882</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.501271</v>
+        <v>-2.50174</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.275</v>
+        <v>-2.281448</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.266993</v>
+        <v>-2.26824</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.706861</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.566947</v>
@@ -2003,7 +2003,7 @@
         <v>0.066638</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.200665</v>
+        <v>0.185637</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>3.289373336814987</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-104.7391781481552</v>
+        <v>16.19391488374284</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.1258</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.037723</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.019931</v>
@@ -2243,28 +2243,28 @@
         <v>1.031715</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.767686</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.007079</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.032345</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.366616</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.039304</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.742395</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.634291</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.382458</v>
       </c>
     </row>
     <row r="35">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.1258</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.037723</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.019931</v>
@@ -2341,28 +2341,28 @@
         <v>1.031715</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.767686</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.007079</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.032345</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.366616</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.039304</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.742395</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.041349</v>
+        <v>0.67564</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.094749</v>
+        <v>1.477207</v>
       </c>
     </row>
     <row r="37">
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.13338</v>
+        <v>0.00758</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.156692</v>
+        <v>0.118969</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>0.062311</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.810275</v>
+        <v>0.042589</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -2938,19 +2938,19 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.396959</v>
+        <v>0.030343</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.149648</v>
+        <v>0.110344</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.807957</v>
+        <v>0.065562</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.634291</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.730801</v>
+        <v>0.348343</v>
       </c>
     </row>
     <row r="49">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -17204,7 +17204,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
@@ -32826,7 +32826,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -34756,7 +34756,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -34842,7 +34842,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -35102,7 +35102,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -36706,7 +36706,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -37488,7 +37488,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -38618,7 +38618,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E369" s="5" t="n">

--- a/output/pdf_financials_xlsx/SRC.xlsx
+++ b/output/pdf_financials_xlsx/SRC.xlsx
@@ -6492,16 +6492,16 @@
         <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0.025</v>
+        <v>2.409476</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>0.579861</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>0.1755</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0</v>
+        <v>0.581</v>
       </c>
       <c r="K120" s="3" t="n">
         <v>0</v>
@@ -24796,7 +24796,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SRC.xlsx
+++ b/output/pdf_financials_xlsx/SRC.xlsx
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.0375</v>
+        <v>0.056262</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.0898</v>
+        <v>0.125631</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.11475</v>
+        <v>0.141756</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.344267</v>
+        <v>0.388597</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.233203</v>
+        <v>0.304008</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.5425</v>
+        <v>0.856877</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.470503</v>
+        <v>0.623793</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -871,10 +871,10 @@
         <v>2.142064</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.121352</v>
+        <v>0.148358</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.3647</v>
+        <v>0.40903</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>2.50174</v>
@@ -924,10 +924,10 @@
         <v>-2.142064</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.121352</v>
+        <v>-0.148358</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.3647</v>
+        <v>-0.40903</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-2.50174</v>
@@ -1239,7 +1239,7 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.05615</v>
+        <v>-0.05615</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -5552,13 +5552,13 @@
         <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004243</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.126279</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.078224</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         <v>-0.076281</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.105189</v>
+        <v>0.100946</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.134994</v>
+        <v>0.008715000000000001</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.156056</v>
+        <v>-0.23428</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0.055018</v>
@@ -19962,7 +19962,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -27630,7 +27634,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -29588,7 +29596,11 @@
           <t>Deferred income taxes recovery</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -30364,7 +30376,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -31980,7 +31996,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -36378,7 +36398,11 @@
           <t>Office expense</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E343" s="5" t="n">
         <v>0.018762</v>
       </c>
@@ -37842,7 +37866,11 @@
           <t>Deferred income tax recovery (note 7)</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -40418,7 +40446,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
